--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484111_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484111_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1501</v>
+        <v>2.3475</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2003</v>
+        <v>3.9768</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0501</v>
+        <v>-1.6293</v>
       </c>
       <c r="G2" t="n">
         <v>3.1325</v>
@@ -610,13 +610,13 @@
         <v>0.9919</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.015</v>
+        <v>-0.8176</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6177</v>
+        <v>0.1588</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.3973</v>
+        <v>-0.9765</v>
       </c>
       <c r="V2" t="n">
         <v>0.4294</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4713</v>
+        <v>-0.1729</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6159</v>
+        <v>1.1681</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1446</v>
+        <v>-1.341</v>
       </c>
       <c r="G3" t="n">
         <v>2.3589</v>
@@ -688,13 +688,13 @@
         <v>0.3968</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6399</v>
+        <v>-0.0043</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6122</v>
+        <v>0.1644</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0277</v>
+        <v>-0.1687</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9405</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1528</v>
+        <v>-0.339</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3338</v>
+        <v>1.2318</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4866</v>
+        <v>-1.5708</v>
       </c>
       <c r="G4" t="n">
         <v>-1.3592</v>
@@ -766,13 +766,13 @@
         <v>0.1984</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0675</v>
+        <v>-0.2537</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4308</v>
+        <v>0.3288</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4983</v>
+        <v>-0.5824</v>
       </c>
       <c r="V4" t="n">
         <v>1.2739</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6888</v>
+        <v>-0.977</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9575</v>
+        <v>0.7534</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6463</v>
+        <v>-1.7304</v>
       </c>
       <c r="G5" t="n">
         <v>0.3041</v>
@@ -844,13 +844,13 @@
         <v>0.1984</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9358</v>
+        <v>0.6476</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6746</v>
+        <v>0.4705</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2612</v>
+        <v>0.1771</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1352</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6039</v>
+        <v>-1.0787</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7454</v>
+        <v>2.0741</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.3492</v>
+        <v>-3.1528</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0156</v>
@@ -922,13 +922,13 @@
         <v>0.9919</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5695</v>
+        <v>-1.0444</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3683</v>
+        <v>-0.0396</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2012</v>
+        <v>-1.0048</v>
       </c>
       <c r="V6" t="n">
         <v>1.3699</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. PARDOS MARTINEZ</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7106</v>
+        <v>-1.6281</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0618</v>
+        <v>-1.9759</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7725</v>
+        <v>0.3478</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9834</v>
+        <v>-1.7273</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5195</v>
+        <v>-0.8619</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4639</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5391</v>
+        <v>-1.8796</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5391</v>
+        <v>-0.5995</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.2801</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4444</v>
+        <v>0.1523</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0195</v>
+        <v>-0.2623</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4639</v>
+        <v>0.4146</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.3968</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4466</v>
+        <v>-0.0992</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9977</v>
+        <v>-0.0963</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.551</v>
+        <v>-0.0029</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1738</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>G. PARDOS MARTINEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0628</v>
+        <v>-2.3104</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2423</v>
+        <v>-0.4256</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1795</v>
+        <v>-1.8847</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7273</v>
+        <v>-1.9834</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8619</v>
+        <v>-0.5195</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8653999999999999</v>
+        <v>-1.4639</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.8796</v>
+        <v>-0.5391</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5995</v>
+        <v>-0.5391</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2801</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1523</v>
+        <v>-1.4444</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2623</v>
+        <v>0.0195</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4146</v>
+        <v>-1.4639</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1984</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.3968</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5339</v>
+        <v>-0.1531</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3627</v>
+        <v>0.5102</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1712</v>
+        <v>-0.6632</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.1738</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1738</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GOMES CORREIA</t>
+          <t>F. VILLALBA KRAMAROV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7049</v>
+        <v>-3.7534</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9547</v>
+        <v>-0.5184</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7502</v>
+        <v>-3.235</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4416</v>
+        <v>0.7086</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1811</v>
+        <v>1.4612</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2605</v>
+        <v>-0.7526</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7528</v>
+        <v>2.5253</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.127</v>
+        <v>1.84</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3742</v>
+        <v>0.6853</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6888</v>
+        <v>-1.8167</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0541</v>
+        <v>-0.3788</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6347</v>
+        <v>-1.4379</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3968</v>
+        <v>-2.579</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1903</v>
+        <v>-3.1741</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0221</v>
+        <v>0.1927</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7937</v>
+        <v>0.1305</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8157</v>
+        <v>0.0622</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8445</v>
+        <v>-2.0757</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1947</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0392</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. VILLALBA KRAMAROV</t>
+          <t>A. GOMES CORREIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.877</v>
+        <v>-3.9563</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0909</v>
+        <v>-1.4025</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7862</v>
+        <v>-2.5539</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7086</v>
+        <v>-2.4416</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4612</v>
+        <v>-2.1811</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7526</v>
+        <v>-0.2605</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5253</v>
+        <v>-0.7528</v>
       </c>
       <c r="K10" t="n">
-        <v>1.84</v>
+        <v>-1.127</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6853</v>
+        <v>0.3742</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8167</v>
+        <v>-1.6888</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3788</v>
+        <v>-1.0541</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4379</v>
+        <v>-0.6347</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.579</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1741</v>
+        <v>-1.1903</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>0.06909999999999999</v>
+        <v>-0.2735</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.442</v>
+        <v>0.3459</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5111</v>
+        <v>-0.6194</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0757</v>
+        <v>-0.8445</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.0757</v>
+        <v>-1.0392</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.2052</v>
+        <v>-6.8929</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0912</v>
+        <v>-4.7228</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.114</v>
+        <v>-2.1701</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5761</v>
@@ -1312,13 +1312,13 @@
         <v>0.1984</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.916</v>
+        <v>-0.6037</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3004</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6156</v>
+        <v>-0.6717</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7293</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.3846</v>
+        <v>-18.7612</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4644000000000004</v>
+        <v>0.1589999999999998</v>
       </c>
       <c r="F12" t="n">
         <v>-18.9202</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5991</v>
+        <v>-2.599099999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>6.728700000000001</v>
+        <v>6.728699999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.327599999999997</v>
+        <v>-9.327599999999999</v>
       </c>
       <c r="J12" t="n">
         <v>8.066899999999999</v>
@@ -1378,7 +1378,7 @@
         <v>-3.509</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.1571</v>
+        <v>-7.157099999999999</v>
       </c>
       <c r="P12" t="n">
         <v>-8.927300000000001</v>
@@ -1387,13 +1387,13 @@
         <v>-13.8868</v>
       </c>
       <c r="R12" t="n">
-        <v>4.959700000000001</v>
+        <v>4.9597</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.0326</v>
+        <v>-2.4092</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4179</v>
+        <v>2.0413</v>
       </c>
       <c r="U12" t="n">
         <v>-4.4503</v>
@@ -1405,7 +1405,7 @@
         <v>3.9376</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.763299999999999</v>
+        <v>-8.763300000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.2463</v>
+        <v>8.0686</v>
       </c>
       <c r="E13" t="n">
-        <v>8.301500000000001</v>
+        <v>7.7913</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0551</v>
+        <v>0.2773</v>
       </c>
       <c r="G13" t="n">
         <v>7.6166</v>
@@ -1468,13 +1468,13 @@
         <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7091</v>
+        <v>0.5314</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3265</v>
+        <v>0.8163</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.2849</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6745</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6442</v>
+        <v>3.713</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5049</v>
+        <v>4.3211</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8606</v>
+        <v>-0.6081</v>
       </c>
       <c r="G14" t="n">
         <v>0.0464</v>
@@ -1546,13 +1546,13 @@
         <v>1.5871</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6681</v>
+        <v>-0.5994</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0599</v>
+        <v>-0.2436</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6083</v>
+        <v>-0.3558</v>
       </c>
       <c r="V14" t="n">
         <v>2.6789</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4263</v>
+        <v>2.1262</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8077</v>
+        <v>1.3996</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6186</v>
+        <v>0.7266</v>
       </c>
       <c r="G15" t="n">
         <v>1.5526</v>
@@ -1624,13 +1624,13 @@
         <v>0.9919</v>
       </c>
       <c r="S15" t="n">
-        <v>1.455</v>
+        <v>1.1549</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3321</v>
+        <v>0.924</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1229</v>
+        <v>0.2309</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5813</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. CUMELLES CESPEDES</t>
+          <t>B. ENRICH TASIAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6372</v>
+        <v>1.4112</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4767</v>
+        <v>0.4099</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1605</v>
+        <v>1.0013</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.5617</v>
+        <v>-0.0864</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.791</v>
+        <v>-0.8871</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2294</v>
+        <v>0.8007</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.0648</v>
+        <v>0.1661</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2681</v>
+        <v>0.0456</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2034</v>
+        <v>0.1205</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4969</v>
+        <v>-0.2525</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5229</v>
+        <v>-0.9327</v>
       </c>
       <c r="O16" t="n">
-        <v>0.026</v>
+        <v>0.6802</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1822</v>
+        <v>0.9919</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1822</v>
+        <v>0.9919</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4033</v>
+        <v>0.6263</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6723</v>
+        <v>0.2438</v>
       </c>
       <c r="U16" t="n">
-        <v>0.731</v>
+        <v>0.3825</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3866</v>
+        <v>-0.1206</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2558</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. ENRICH TASIAS</t>
+          <t>M. BENITO MULLERAT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0592</v>
+        <v>1.1287</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0018</v>
+        <v>0.8374</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0574</v>
+        <v>0.2913</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0864</v>
+        <v>-1.441</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8871</v>
+        <v>-0.7763</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8007</v>
+        <v>-0.6646</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1661</v>
+        <v>-0.2161</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0456</v>
+        <v>0.3385</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1205</v>
+        <v>-0.5546</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2525</v>
+        <v>-1.2248</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9327</v>
+        <v>-1.1148</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6802</v>
+        <v>-0.11</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2743</v>
+        <v>0.0539</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1643</v>
+        <v>0.5216</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4387</v>
+        <v>-0.4677</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1206</v>
+        <v>0.532</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ALIAGA CHECA</t>
+          <t>A. LATORRE SEGURA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9530999999999999</v>
+        <v>1.0228</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1172</v>
+        <v>0.8653</v>
       </c>
       <c r="F18" t="n">
-        <v>0.836</v>
+        <v>0.1575</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5572</v>
+        <v>0.8386</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4639</v>
+        <v>-0.2924</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.09329999999999999</v>
+        <v>1.131</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5112</v>
+        <v>0.7632</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1263</v>
+        <v>0.0403</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6375</v>
+        <v>0.7229</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.046</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.3328</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5442</v>
+        <v>0.4081</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2181</v>
+        <v>-0.0142</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4058</v>
+        <v>0.102</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1877</v>
+        <v>-0.1162</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0858</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. BENITO MULLERAT</t>
+          <t>E. TEJERO CASASAYAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9366</v>
+        <v>0.7843</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8374</v>
+        <v>0.9787</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09909999999999999</v>
+        <v>-0.1944</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.441</v>
+        <v>-2.2702</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7763</v>
+        <v>-1.3205</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6646</v>
+        <v>-0.9497</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2161</v>
+        <v>-0.8963</v>
       </c>
       <c r="K19" t="n">
         <v>0.3385</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5546</v>
+        <v>-1.2348</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2248</v>
+        <v>-1.3739</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1148</v>
+        <v>-1.659</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.11</v>
+        <v>0.2851</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9838</v>
+        <v>2.579</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9838</v>
+        <v>2.579</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1383</v>
+        <v>-0.0071</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5216</v>
+        <v>0.4026</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6599</v>
+        <v>-0.4096</v>
       </c>
       <c r="V19" t="n">
-        <v>0.532</v>
+        <v>0.4826</v>
       </c>
       <c r="W19" t="n">
-        <v>0.532</v>
+        <v>1.4724</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.9899</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LATORRE SEGURA</t>
+          <t>M. ALIAGA CHECA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8646</v>
+        <v>0.6292</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7632</v>
+        <v>-0.2909</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1014</v>
+        <v>0.9201</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8386</v>
+        <v>-0.5572</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2924</v>
+        <v>-0.4639</v>
       </c>
       <c r="I20" t="n">
-        <v>1.131</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7632</v>
+        <v>-0.5112</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0403</v>
+        <v>0.1263</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7229</v>
+        <v>-0.6375</v>
       </c>
       <c r="M20" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.046</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3328</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4081</v>
+        <v>0.5442</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1723</v>
+        <v>0.8942</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.9977</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1723</v>
+        <v>-0.1035</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.0858</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3704</v>
+        <v>0.5243</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0293</v>
+        <v>2.1313</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6588</v>
+        <v>-1.607</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6293</v>
@@ -2092,13 +2092,13 @@
         <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4132</v>
+        <v>-0.2593</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0679</v>
+        <v>0.0341</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3453</v>
+        <v>-0.2934</v>
       </c>
       <c r="V21" t="n">
         <v>1.8097</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. RIERA PERETO</t>
+          <t>A. CUMELLES CESPEDES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.128</v>
+        <v>0.3704</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0202</v>
+        <v>0.3544</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1079</v>
+        <v>0.016</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0906</v>
+        <v>-2.5617</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1815</v>
+        <v>-2.791</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2721</v>
+        <v>0.2294</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0202</v>
+        <v>-1.0648</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0202</v>
+        <v>-1.2681</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.2034</v>
       </c>
       <c r="M22" t="n">
-        <v>0.07049999999999999</v>
+        <v>-1.4969</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2016</v>
+        <v>-1.5229</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2721</v>
+        <v>0.026</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.1822</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.1822</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0374</v>
+        <v>1.1365</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0374</v>
+        <v>0.5865</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3866</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2558</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. TEJERO CASASAYAS</t>
+          <t>O. RIERA PERETO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1185</v>
+        <v>0.2862</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0604</v>
+        <v>0.1222</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0581</v>
+        <v>0.164</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2702</v>
+        <v>0.0906</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3205</v>
+        <v>-0.1815</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9497</v>
+        <v>0.2721</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8963</v>
+        <v>0.0202</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3385</v>
+        <v>0.0202</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2348</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3739</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.659</v>
+        <v>-0.2016</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2851</v>
+        <v>0.2721</v>
       </c>
       <c r="P23" t="n">
-        <v>2.579</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.579</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6728</v>
+        <v>0.1955</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5157</v>
+        <v>0.102</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1571</v>
+        <v>0.0935</v>
       </c>
       <c r="V23" t="n">
-        <v>0.4826</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.9899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>19.3844</v>
+        <v>20.0649</v>
       </c>
       <c r="E24" t="n">
         <v>18.9203</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4644999999999995</v>
+        <v>1.1446</v>
       </c>
       <c r="G24" t="n">
-        <v>2.599</v>
+        <v>2.599000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-6.7286</v>
@@ -2305,7 +2305,7 @@
         <v>3.5092</v>
       </c>
       <c r="L24" t="n">
-        <v>7.157099999999998</v>
+        <v>7.1571</v>
       </c>
       <c r="M24" t="n">
         <v>-8.067</v>
@@ -2326,19 +2326,19 @@
         <v>13.8869</v>
       </c>
       <c r="S24" t="n">
-        <v>3.0325</v>
+        <v>3.7127</v>
       </c>
       <c r="T24" t="n">
-        <v>4.4505</v>
+        <v>4.4504</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.418</v>
+        <v>-0.7376999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>4.826</v>
+        <v>4.826000000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>8.763400000000001</v>
+        <v>8.763399999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-3.9374</v>
